--- a/m2/exemplos/analise-vendas/insumo-vendas-20-lojas-30-dias.xlsx
+++ b/m2/exemplos/analise-vendas/insumo-vendas-20-lojas-30-dias.xlsx
@@ -26708,22 +26708,22 @@
         </is>
       </c>
       <c r="F583" s="3" t="n">
-        <v>6696.72</v>
+        <v>4018.03</v>
       </c>
       <c r="G583" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H583" s="2" t="n">
-        <v>288</v>
+        <v>173</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="K583" s="2" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="584">
@@ -26753,22 +26753,22 @@
         </is>
       </c>
       <c r="F584" s="3" t="n">
-        <v>3920.87</v>
+        <v>2352.52</v>
       </c>
       <c r="G584" s="3" t="n">
         <v>25.22</v>
       </c>
       <c r="H584" s="2" t="n">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="I584" s="2" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="J584" s="2" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="K584" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="585">
@@ -26798,22 +26798,22 @@
         </is>
       </c>
       <c r="F585" s="3" t="n">
-        <v>4925.26</v>
+        <v>2955.16</v>
       </c>
       <c r="G585" s="3" t="n">
         <v>26</v>
       </c>
       <c r="H585" s="2" t="n">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="K585" s="2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="586">
@@ -26843,22 +26843,22 @@
         </is>
       </c>
       <c r="F586" s="3" t="n">
-        <v>4944.29</v>
+        <v>2966.57</v>
       </c>
       <c r="G586" s="3" t="n">
         <v>24.16</v>
       </c>
       <c r="H586" s="2" t="n">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="I586" s="2" t="n">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="J586" s="2" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="K586" s="2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="587">
@@ -26888,22 +26888,22 @@
         </is>
       </c>
       <c r="F587" s="3" t="n">
-        <v>4747.27</v>
+        <v>2848.36</v>
       </c>
       <c r="G587" s="3" t="n">
         <v>23.32</v>
       </c>
       <c r="H587" s="2" t="n">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="K587" s="2" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="588">
@@ -26933,22 +26933,22 @@
         </is>
       </c>
       <c r="F588" s="3" t="n">
-        <v>6413.67</v>
+        <v>3848.2</v>
       </c>
       <c r="G588" s="3" t="n">
         <v>25.66</v>
       </c>
       <c r="H588" s="2" t="n">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="I588" s="2" t="n">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="J588" s="2" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="K588" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="589">
@@ -26978,22 +26978,22 @@
         </is>
       </c>
       <c r="F589" s="3" t="n">
-        <v>6832.23</v>
+        <v>4099.34</v>
       </c>
       <c r="G589" s="3" t="n">
         <v>24.44</v>
       </c>
       <c r="H589" s="2" t="n">
-        <v>279</v>
+        <v>167</v>
       </c>
       <c r="I589" s="2" t="n">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="J589" s="2" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="K589" s="2" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="590">
@@ -27023,22 +27023,22 @@
         </is>
       </c>
       <c r="F590" s="3" t="n">
-        <v>6240.53</v>
+        <v>3744.32</v>
       </c>
       <c r="G590" s="3" t="n">
         <v>23.79</v>
       </c>
       <c r="H590" s="2" t="n">
-        <v>262</v>
+        <v>157</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="K590" s="2" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="591">
